--- a/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
+++ b/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9273850-E85D-4FE8-B068-D0DD484E7F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4176D3-7BE8-47D7-A6AF-10F44366DFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataSet" sheetId="1" r:id="rId1"/>

--- a/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
+++ b/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4176D3-7BE8-47D7-A6AF-10F44366DFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375B33FD-E3A0-4984-8544-E9478024E7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="705">
   <si>
     <t>UserName</t>
   </si>
@@ -2177,6 +2177,9 @@
   </si>
   <si>
     <t>5VR72G68E2565U77E63D</t>
+  </si>
+  <si>
+    <t>Product_3QTY</t>
   </si>
 </sst>
 </file>
@@ -2730,7 +2733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW75"/>
+  <dimension ref="A1:AW76"/>
   <sheetFormatPr defaultColWidth="56.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
@@ -3626,21 +3629,28 @@
         <v>694</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>603</v>
+        <v>704</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="AC23" s="42" t="s">
-        <v>600</v>
-      </c>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="22"/>
+        <v>538</v>
+      </c>
+      <c r="AD23" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="AE23" s="22" t="s">
+        <v>587</v>
+      </c>
+      <c r="AF23" s="22" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="24" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -3652,233 +3662,213 @@
     </row>
     <row r="25" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="AC25" s="42"/>
-      <c r="AD25" s="32" t="s">
-        <v>597</v>
-      </c>
+      <c r="AC25" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="AD25" s="32"/>
       <c r="AE25" s="22"/>
     </row>
     <row r="26" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="AC26" s="42"/>
       <c r="AD26" s="32" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AE26" s="22"/>
     </row>
     <row r="27" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="AC27" s="42"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="22" t="s">
-        <v>589</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AD27" s="32" t="s">
+        <v>599</v>
+      </c>
+      <c r="AE27" s="22"/>
+    </row>
+    <row r="28" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>440</v>
+        <v>588</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="AC28" t="s">
-        <v>177</v>
-      </c>
-      <c r="AD28" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>177</v>
+      <c r="AC28" s="42"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="22" t="s">
+        <v>589</v>
       </c>
       <c r="AF28" t="s">
-        <v>39</v>
+        <v>610</v>
       </c>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>440</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="AC29" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AD29" s="5" t="s">
         <v>120</v>
       </c>
+      <c r="AE29" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="AD30" s="5"/>
-      <c r="AF30" t="s">
-        <v>259</v>
+      <c r="AC30" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD30" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="AL31" s="12" t="s">
-        <v>442</v>
+      <c r="AD31" s="5"/>
+      <c r="AF31" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>32</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="AD32" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="AL32" s="12" t="s">
-        <v>585</v>
+        <v>442</v>
       </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="H33" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="I33" s="2"/>
-      <c r="AH33">
-        <v>3</v>
+      <c r="AD33" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL33" s="12" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="G34" s="6"/>
+        <v>40</v>
+      </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="Z34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA34" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="AB34">
-        <v>123</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>478</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>579</v>
+      <c r="AH34">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
-      </c>
-      <c r="S35" t="s">
-        <v>150</v>
-      </c>
-      <c r="T35" t="s">
-        <v>17</v>
-      </c>
-      <c r="V35" t="s">
-        <v>19</v>
-      </c>
-      <c r="W35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="X35" s="5" t="s">
-        <v>59</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
       <c r="Z35" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA35" s="7" t="s">
         <v>439</v>
       </c>
       <c r="AB35">
-        <v>1234</v>
+        <v>123</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>478</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>46</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="S36" t="s">
+        <v>150</v>
+      </c>
+      <c r="T36" t="s">
+        <v>17</v>
+      </c>
+      <c r="V36" t="s">
+        <v>19</v>
+      </c>
+      <c r="W36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="X36" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="Z36" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA36" s="7" t="s">
         <v>439</v>
       </c>
       <c r="AB36">
-        <v>123</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="S37" t="s">
-        <v>150</v>
-      </c>
-      <c r="T37" t="s">
-        <v>17</v>
-      </c>
-      <c r="V37" t="s">
-        <v>19</v>
-      </c>
-      <c r="W37" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="X37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y37" s="5" t="s">
-        <v>52</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
       <c r="Z37" s="5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="AA37" s="7" t="s">
         <v>439</v>
@@ -3886,53 +3876,53 @@
       <c r="AB37">
         <v>123</v>
       </c>
-      <c r="AK37" s="5" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="S38" t="s">
+        <v>150</v>
+      </c>
+      <c r="T38" t="s">
+        <v>17</v>
+      </c>
+      <c r="V38" t="s">
+        <v>19</v>
+      </c>
+      <c r="W38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="X38" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y38" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="Z38" s="5" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="AA38" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB38" s="5">
-        <v>1</v>
+        <v>439</v>
+      </c>
+      <c r="AB38">
+        <v>123</v>
+      </c>
+      <c r="AK38" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>55</v>
-      </c>
-      <c r="S39" t="s">
-        <v>492</v>
-      </c>
-      <c r="T39" t="s">
-        <v>494</v>
-      </c>
-      <c r="U39" t="s">
-        <v>485</v>
-      </c>
-      <c r="V39" t="s">
-        <v>493</v>
-      </c>
-      <c r="W39" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="X39" s="5" t="s">
-        <v>59</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F39" t="s">
+        <v>50</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="2"/>
       <c r="Z39" s="5" t="s">
         <v>56</v>
       </c>
@@ -3945,13 +3935,7 @@
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="S40" t="s">
         <v>492</v>
@@ -3971,112 +3955,117 @@
       <c r="X40" s="5" t="s">
         <v>59</v>
       </c>
+      <c r="Z40" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA40" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB40" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="W41" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="S41" t="s">
+        <v>492</v>
+      </c>
+      <c r="T41" t="s">
+        <v>494</v>
+      </c>
+      <c r="U41" t="s">
+        <v>485</v>
+      </c>
+      <c r="V41" t="s">
+        <v>493</v>
+      </c>
+      <c r="W41" s="5" t="s">
+        <v>495</v>
+      </c>
       <c r="X41" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="E42" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="H42" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="S42" t="s">
-        <v>492</v>
-      </c>
-      <c r="T42" t="s">
-        <v>494</v>
-      </c>
-      <c r="U42" t="s">
-        <v>485</v>
-      </c>
-      <c r="V42" t="s">
-        <v>493</v>
-      </c>
-      <c r="W42" s="5" t="s">
-        <v>495</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="W42" s="5"/>
       <c r="X42" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL43" t="s">
-        <v>434</v>
+        <v>77</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="H43" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="S43" t="s">
+        <v>492</v>
+      </c>
+      <c r="T43" t="s">
+        <v>494</v>
+      </c>
+      <c r="U43" t="s">
+        <v>485</v>
+      </c>
+      <c r="V43" t="s">
+        <v>493</v>
+      </c>
+      <c r="W43" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="X43" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>118</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>15</v>
       </c>
       <c r="AL44" t="s">
-        <v>582</v>
-      </c>
-      <c r="AM44" t="s">
-        <v>295</v>
-      </c>
-      <c r="AN44" t="s">
-        <v>313</v>
-      </c>
-      <c r="AO44" t="s">
-        <v>313</v>
+        <v>434</v>
       </c>
     </row>
     <row r="45" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>164</v>
-      </c>
-      <c r="R45" s="12"/>
-      <c r="S45" t="s">
-        <v>492</v>
-      </c>
-      <c r="T45" t="s">
-        <v>494</v>
-      </c>
-      <c r="U45" t="s">
-        <v>485</v>
-      </c>
-      <c r="V45" t="s">
-        <v>493</v>
-      </c>
-      <c r="W45" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="X45" s="5" t="s">
-        <v>59</v>
+        <v>151</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>582</v>
       </c>
       <c r="AM45" t="s">
         <v>295</v>
@@ -4090,76 +4079,98 @@
     </row>
     <row r="46" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>166</v>
-      </c>
-      <c r="F46" t="s">
-        <v>167</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="12"/>
-      <c r="AC46" t="s">
-        <v>257</v>
-      </c>
-      <c r="AP46" t="s">
-        <v>186</v>
+        <v>164</v>
+      </c>
+      <c r="R46" s="12"/>
+      <c r="S46" t="s">
+        <v>492</v>
+      </c>
+      <c r="T46" t="s">
+        <v>494</v>
+      </c>
+      <c r="U46" t="s">
+        <v>485</v>
+      </c>
+      <c r="V46" t="s">
+        <v>493</v>
+      </c>
+      <c r="W46" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="X46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>295</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>313</v>
+      </c>
+      <c r="AO46" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>184</v>
-      </c>
-      <c r="H47" s="23" t="s">
-        <v>591</v>
+        <v>166</v>
+      </c>
+      <c r="F47" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="12"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="12"/>
+      <c r="AC47" t="s">
+        <v>257</v>
+      </c>
       <c r="AP47" t="s">
-        <v>279</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>278</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="H48" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="I48" s="12"/>
       <c r="AP48" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>283</v>
-      </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC49" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD49" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ49" t="s">
-        <v>83</v>
+        <v>278</v>
+      </c>
+      <c r="AP49" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>215</v>
+        <v>283</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>255</v>
+      </c>
+      <c r="AD50" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="AF50" t="s">
         <v>39</v>
@@ -4167,56 +4178,59 @@
       <c r="AQ50" t="s">
         <v>83</v>
       </c>
-      <c r="AR50" t="s">
-        <v>216</v>
-      </c>
-      <c r="AS50" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="51" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>209</v>
-      </c>
-      <c r="R51" s="5"/>
+        <v>215</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ51" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>216</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="52" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>601</v>
-      </c>
-      <c r="P52" t="s">
-        <v>602</v>
+        <v>209</v>
       </c>
       <c r="R52" s="5"/>
     </row>
     <row r="53" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>338</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="O53" t="s">
-        <v>340</v>
-      </c>
-      <c r="P53" s="26" t="s">
-        <v>566</v>
-      </c>
-      <c r="Q53" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="R53" t="s">
-        <v>344</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="P53" t="s">
+        <v>602</v>
+      </c>
+      <c r="R53" s="5"/>
     </row>
     <row r="54" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>342</v>
+        <v>338</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="O54" t="s">
+        <v>340</v>
+      </c>
+      <c r="P54" s="26" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>354</v>
       </c>
       <c r="R54" t="s">
         <v>344</v>
@@ -4224,157 +4238,136 @@
     </row>
     <row r="55" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>345</v>
-      </c>
-      <c r="L55" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="M55" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="N55" s="24" t="s">
-        <v>497</v>
-      </c>
-      <c r="AP55" t="s">
-        <v>350</v>
+        <v>342</v>
+      </c>
+      <c r="R55" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="56" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>347</v>
-      </c>
-      <c r="F56" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" t="s">
-        <v>348</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>500</v>
+        <v>345</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="N56" s="24" t="s">
+        <v>497</v>
       </c>
       <c r="AP56" t="s">
-        <v>590</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>352</v>
-      </c>
-      <c r="P57" s="26" t="s">
-        <v>567</v>
+        <v>347</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>348</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="AP57" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="58" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>569</v>
+        <v>352</v>
       </c>
       <c r="P58" s="26" t="s">
-        <v>570</v>
-      </c>
-      <c r="S58" t="s">
-        <v>492</v>
-      </c>
-      <c r="T58" t="s">
-        <v>494</v>
-      </c>
-      <c r="U58" t="s">
-        <v>485</v>
-      </c>
-      <c r="V58" t="s">
-        <v>493</v>
-      </c>
-      <c r="W58" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="X58" s="5" t="s">
-        <v>59</v>
+        <v>567</v>
       </c>
     </row>
     <row r="59" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>201</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" t="s">
-        <v>348</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>304</v>
+        <v>569</v>
+      </c>
+      <c r="P59" s="26" t="s">
+        <v>570</v>
+      </c>
+      <c r="S59" t="s">
+        <v>492</v>
+      </c>
+      <c r="T59" t="s">
+        <v>494</v>
+      </c>
+      <c r="U59" t="s">
+        <v>485</v>
+      </c>
+      <c r="V59" t="s">
+        <v>493</v>
+      </c>
+      <c r="W59" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="X59" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>362</v>
-      </c>
-      <c r="P60" s="26" t="s">
-        <v>565</v>
+        <v>201</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>348</v>
+      </c>
+      <c r="H60" s="12" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="61" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>430</v>
-      </c>
-      <c r="P61" s="27" t="s">
-        <v>696</v>
+        <v>362</v>
+      </c>
+      <c r="P61" s="26" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="62" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>431</v>
-      </c>
-      <c r="P62" s="26" t="s">
-        <v>699</v>
-      </c>
-      <c r="AU62" t="s">
-        <v>513</v>
-      </c>
-      <c r="AV62" s="31" t="s">
-        <v>232</v>
+        <v>430</v>
+      </c>
+      <c r="P62" s="27" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="63" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>431</v>
+      </c>
+      <c r="P63" s="26" t="s">
+        <v>699</v>
+      </c>
+      <c r="AU63" t="s">
+        <v>513</v>
+      </c>
+      <c r="AV63" s="31" t="s">
         <v>232</v>
-      </c>
-      <c r="R63" s="33"/>
-      <c r="S63" s="33"/>
-      <c r="T63" s="33"/>
-      <c r="U63" s="33"/>
-      <c r="V63" s="33"/>
-      <c r="W63" s="33"/>
-      <c r="X63" s="33"/>
-      <c r="Y63" s="33"/>
-      <c r="Z63" s="33"/>
-      <c r="AA63" s="33"/>
-      <c r="AB63" s="33"/>
-      <c r="AC63" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD63" s="33">
-        <v>1</v>
-      </c>
-      <c r="AE63" s="33"/>
-      <c r="AU63" t="s">
-        <v>692</v>
-      </c>
-      <c r="AV63" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>634</v>
+        <v>232</v>
       </c>
       <c r="R64" s="33"/>
       <c r="S64" s="33"/>
@@ -4387,11 +4380,15 @@
       <c r="Z64" s="33"/>
       <c r="AA64" s="33"/>
       <c r="AB64" s="33"/>
-      <c r="AC64" s="33"/>
-      <c r="AD64" s="33"/>
+      <c r="AC64" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD64" s="33">
+        <v>1</v>
+      </c>
       <c r="AE64" s="33"/>
       <c r="AU64" t="s">
-        <v>635</v>
+        <v>692</v>
       </c>
       <c r="AV64" t="s">
         <v>315</v>
@@ -4399,7 +4396,7 @@
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="R65" s="33"/>
       <c r="S65" s="33"/>
@@ -4416,15 +4413,15 @@
       <c r="AD65" s="33"/>
       <c r="AE65" s="33"/>
       <c r="AU65" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="AV65" t="s">
-        <v>638</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="R66" s="33"/>
       <c r="S66" s="33"/>
@@ -4441,132 +4438,157 @@
       <c r="AD66" s="33"/>
       <c r="AE66" s="33"/>
       <c r="AU66" t="s">
+        <v>639</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>640</v>
+      </c>
+      <c r="R67" s="33"/>
+      <c r="S67" s="33"/>
+      <c r="T67" s="33"/>
+      <c r="U67" s="33"/>
+      <c r="V67" s="33"/>
+      <c r="W67" s="33"/>
+      <c r="X67" s="33"/>
+      <c r="Y67" s="33"/>
+      <c r="Z67" s="33"/>
+      <c r="AA67" s="33"/>
+      <c r="AB67" s="33"/>
+      <c r="AC67" s="33"/>
+      <c r="AD67" s="33"/>
+      <c r="AE67" s="33"/>
+      <c r="AU67" t="s">
         <v>642</v>
       </c>
-      <c r="AV66" t="s">
+      <c r="AV67" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A67" s="33" t="s">
+    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A68" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="33"/>
-      <c r="I67" s="33"/>
-      <c r="J67" s="33"/>
-      <c r="K67" s="33"/>
-      <c r="L67" s="33"/>
-      <c r="M67" s="33"/>
-      <c r="N67" s="33"/>
-      <c r="O67" s="33"/>
-      <c r="P67" s="33"/>
-      <c r="Q67" s="33"/>
-    </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>444</v>
-      </c>
-      <c r="P68" s="26" t="s">
-        <v>697</v>
-      </c>
+      <c r="B68" s="33"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="33"/>
+      <c r="F68" s="33"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="33"/>
+      <c r="N68" s="33"/>
+      <c r="O68" s="33"/>
+      <c r="P68" s="33"/>
+      <c r="Q68" s="33"/>
     </row>
     <row r="69" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>444</v>
+      </c>
+      <c r="P69" s="26" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>499</v>
       </c>
-      <c r="P69" s="26" t="s">
+      <c r="P70" s="26" t="s">
         <v>568</v>
       </c>
-      <c r="S69" t="s">
+      <c r="S70" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="70" spans="1:48" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>508</v>
-      </c>
-      <c r="AC70" s="42"/>
     </row>
     <row r="71" spans="1:48" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>508</v>
+      </c>
+      <c r="AC71" s="42"/>
+    </row>
+    <row r="72" spans="1:48" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>511</v>
       </c>
-      <c r="AC71" s="42" t="s">
+      <c r="AC72" s="42" t="s">
         <v>636</v>
-      </c>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>515</v>
-      </c>
-      <c r="P72" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>605</v>
+        <v>515</v>
       </c>
       <c r="P73" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="74" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>701</v>
+        <v>605</v>
       </c>
       <c r="P74" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>701</v>
+      </c>
+      <c r="P75" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>702</v>
       </c>
-      <c r="P75" t="s">
+      <c r="P76" t="s">
         <v>703</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{92F09EC2-FC6F-443B-965E-DCA7B56F1753}"/>
-    <hyperlink ref="D32" r:id="rId2" display="Lotuswave@123" xr:uid="{27A376CC-4E23-4441-B806-FE9FF359794E}"/>
+    <hyperlink ref="D33" r:id="rId2" display="Lotuswave@123" xr:uid="{27A376CC-4E23-4441-B806-FE9FF359794E}"/>
     <hyperlink ref="E2" r:id="rId3" xr:uid="{5B310480-7344-4661-AB0F-D7D61F727B40}"/>
-    <hyperlink ref="H38" r:id="rId4" xr:uid="{D3AC8605-ACE0-4742-A275-CC55BA0B713E}"/>
-    <hyperlink ref="H42" r:id="rId5" xr:uid="{EBF04138-1F63-4113-A63D-68EC86409EAF}"/>
-    <hyperlink ref="AL31" r:id="rId6" xr:uid="{C3ED735C-0638-4013-B1A9-35D874D27CCD}"/>
-    <hyperlink ref="H46" r:id="rId7" xr:uid="{7B92FAF6-FC7B-4378-BAA5-F455D3557016}"/>
+    <hyperlink ref="H39" r:id="rId4" xr:uid="{D3AC8605-ACE0-4742-A275-CC55BA0B713E}"/>
+    <hyperlink ref="H43" r:id="rId5" xr:uid="{EBF04138-1F63-4113-A63D-68EC86409EAF}"/>
+    <hyperlink ref="AL32" r:id="rId6" xr:uid="{C3ED735C-0638-4013-B1A9-35D874D27CCD}"/>
+    <hyperlink ref="H47" r:id="rId7" xr:uid="{7B92FAF6-FC7B-4378-BAA5-F455D3557016}"/>
     <hyperlink ref="D2" r:id="rId8" xr:uid="{6D9C84C2-080E-49A8-91A9-0C4040F17B99}"/>
-    <hyperlink ref="H47" r:id="rId9" display="Hfemeanewaccount@gmail.com" xr:uid="{5EDA0D22-59C6-4E86-B1C8-F3DDADDA222C}"/>
+    <hyperlink ref="H48" r:id="rId9" display="Hfemeanewaccount@gmail.com" xr:uid="{5EDA0D22-59C6-4E86-B1C8-F3DDADDA222C}"/>
     <hyperlink ref="B2" r:id="rId10" xr:uid="{49EA4C67-65EF-4ECE-B592-DD27DDBFE9D8}"/>
     <hyperlink ref="I2" r:id="rId11" xr:uid="{41758504-FDAA-49B8-A517-3CF2E58C91CC}"/>
     <hyperlink ref="C2" r:id="rId12" xr:uid="{12FE48FE-6D5F-46FF-BB71-C2756AE73EE8}"/>
     <hyperlink ref="D3" r:id="rId13" xr:uid="{62C3648F-7D52-4B9F-ADF3-7CB24D30FA17}"/>
     <hyperlink ref="E3" r:id="rId14" xr:uid="{32229FD5-4AFA-45C3-BF60-2566B7569180}"/>
     <hyperlink ref="AC19" r:id="rId15" display="https://mcloud-na-preprod.hydroflask.com/wide-mouth-flex-cap?color=Black" xr:uid="{618667E2-3380-4A1C-B34F-ABDD50D4EE61}"/>
-    <hyperlink ref="H56" r:id="rId16" xr:uid="{7BF19D0A-861B-44DA-ABCD-EB14EC4082CF}"/>
-    <hyperlink ref="H59" r:id="rId17" xr:uid="{7332F9F7-6E5B-4009-8325-28D766EC646E}"/>
+    <hyperlink ref="H57" r:id="rId16" xr:uid="{7BF19D0A-861B-44DA-ABCD-EB14EC4082CF}"/>
+    <hyperlink ref="H60" r:id="rId17" xr:uid="{7332F9F7-6E5B-4009-8325-28D766EC646E}"/>
     <hyperlink ref="E6" r:id="rId18" xr:uid="{2C317B8E-AF32-4D4C-AE44-1F2FC9B108BE}"/>
     <hyperlink ref="D6" r:id="rId19" xr:uid="{E6081600-960B-4A22-B355-F1C4E40470AA}"/>
     <hyperlink ref="B6" r:id="rId20" xr:uid="{7D100C12-0453-4673-AC35-2EA4A2603564}"/>
     <hyperlink ref="I6" r:id="rId21" display="LotusQA.GLD.PR.HYF.AutoTest7@gmail.com" xr:uid="{4380A0E0-76DF-485C-8BEA-6C28F9B24971}"/>
     <hyperlink ref="C6" r:id="rId22" display="LotusQA.GLD.PR.HYF.AutoTest7@gmail.com" xr:uid="{8F318BE4-05CB-41C2-8BFD-E5C42814E494}"/>
     <hyperlink ref="H6" r:id="rId23" xr:uid="{407C8F4E-9B49-4856-B5B1-AADA1B530463}"/>
-    <hyperlink ref="D41" r:id="rId24" xr:uid="{CFA846D7-1044-49EA-A0C9-5358EDB0782D}"/>
+    <hyperlink ref="D42" r:id="rId24" xr:uid="{CFA846D7-1044-49EA-A0C9-5358EDB0782D}"/>
     <hyperlink ref="H4" r:id="rId25" xr:uid="{D910C898-EA43-409E-B04E-9B9BFB5A3D9D}"/>
     <hyperlink ref="E4" r:id="rId26" xr:uid="{B86A9B6C-A653-4B11-A92A-B12ECCF56B54}"/>
     <hyperlink ref="D4" r:id="rId27" xr:uid="{5357CB07-F4C9-42F8-8AA6-82DE7438DA1F}"/>
     <hyperlink ref="B4" r:id="rId28" xr:uid="{6B5AE7EC-0874-471E-8B2A-119BB6055DFF}"/>
     <hyperlink ref="I4" r:id="rId29" xr:uid="{C425EF67-01D4-42EC-8E86-0A6DFDCBD4BA}"/>
     <hyperlink ref="C4" r:id="rId30" xr:uid="{50F1E974-01BC-40BB-A015-3C5D601540DD}"/>
-    <hyperlink ref="H41" r:id="rId31" display="Hfemeanewaccount@gmail.com" xr:uid="{EDD9788C-AEBE-4F86-8A6C-8043A32B81A6}"/>
-    <hyperlink ref="I41" r:id="rId32" display="Hfemeanewaccount@gmail.com" xr:uid="{68882096-6651-4D29-9355-6F1410B100AA}"/>
+    <hyperlink ref="H42" r:id="rId31" display="Hfemeanewaccount@gmail.com" xr:uid="{EDD9788C-AEBE-4F86-8A6C-8043A32B81A6}"/>
+    <hyperlink ref="I42" r:id="rId32" display="Hfemeanewaccount@gmail.com" xr:uid="{68882096-6651-4D29-9355-6F1410B100AA}"/>
     <hyperlink ref="H8" r:id="rId33" xr:uid="{867EC1A7-B881-422A-8354-C1C7FCE40AAE}"/>
     <hyperlink ref="E8" r:id="rId34" xr:uid="{5ACEF6FA-BF68-4BBD-BE65-3578FCD63C44}"/>
     <hyperlink ref="D8" r:id="rId35" xr:uid="{3607587D-2F3E-4312-8C6F-F1EF148F7A1A}"/>
@@ -4588,9 +4610,9 @@
     <hyperlink ref="B10" r:id="rId51" xr:uid="{17E9DB6C-30D3-4F48-81EA-C35AF660B980}"/>
     <hyperlink ref="I10" r:id="rId52" xr:uid="{797DAE89-D941-4743-B597-439A5C30AAF0}"/>
     <hyperlink ref="C10" r:id="rId53" xr:uid="{34EC3537-EEF4-4D6F-923E-4AE4713BD831}"/>
-    <hyperlink ref="D59" r:id="rId54" xr:uid="{D9B3D2C8-8647-42D9-A4A0-095F61674861}"/>
+    <hyperlink ref="D60" r:id="rId54" xr:uid="{D9B3D2C8-8647-42D9-A4A0-095F61674861}"/>
     <hyperlink ref="H13" r:id="rId55" xr:uid="{E9756DE8-6826-41D1-9FFA-8650413C0FFA}"/>
-    <hyperlink ref="AL32" r:id="rId56" xr:uid="{277537F5-68B0-41F9-AB74-A5237DB228B6}"/>
+    <hyperlink ref="AL33" r:id="rId56" xr:uid="{277537F5-68B0-41F9-AB74-A5237DB228B6}"/>
     <hyperlink ref="B3" r:id="rId57" xr:uid="{150B5483-771D-49C8-8086-2BA53FC3ED08}"/>
     <hyperlink ref="H3" r:id="rId58" xr:uid="{195D6A3E-A949-43F0-8B40-48EAF4295DC3}"/>
     <hyperlink ref="C3" r:id="rId59" xr:uid="{E3D4A2D5-A63D-402B-9143-60103D9905D4}"/>

--- a/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
+++ b/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375B33FD-E3A0-4984-8544-E9478024E7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C07D09-9C6D-4E30-943C-E400EDC6218F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataSet" sheetId="1" r:id="rId1"/>
@@ -1772,9 +1772,6 @@
     <t>Caps &amp; Lids​,Bottle Boots,Cleaning &amp; Care​</t>
   </si>
   <si>
-    <t>Bestsellers</t>
-  </si>
-  <si>
     <t>Food Jars,Insulated Totes,Soft Coolers ,Outdoor Kitchen</t>
   </si>
   <si>
@@ -1921,9 +1918,6 @@
     <t>coolers</t>
   </si>
   <si>
-    <t>Our Story,FAQ,Contact,Refill For Good,Blog,Festival Partnerships</t>
-  </si>
-  <si>
     <t>shop-by-activity</t>
   </si>
   <si>
@@ -2180,6 +2174,12 @@
   </si>
   <si>
     <t>Product_3QTY</t>
+  </si>
+  <si>
+    <t>Best Sellers</t>
+  </si>
+  <si>
+    <t>Our Story,FAQ,Contact,Refill For Good,Blog</t>
   </si>
 </sst>
 </file>
@@ -2969,10 +2969,10 @@
         <v>293</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>29</v>
@@ -2987,10 +2987,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -3082,10 +3082,10 @@
         <v>358</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
@@ -3100,10 +3100,10 @@
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3454,10 +3454,10 @@
         <v>64</v>
       </c>
       <c r="P13" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q13" s="5" t="s">
         <v>580</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>581</v>
       </c>
       <c r="T13" t="s">
         <v>332</v>
@@ -3466,10 +3466,10 @@
         <v>64</v>
       </c>
       <c r="V13" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="W13" s="5" t="s">
         <v>580</v>
-      </c>
-      <c r="W13" s="5" t="s">
-        <v>581</v>
       </c>
       <c r="Z13" s="5" t="s">
         <v>297</v>
@@ -3517,7 +3517,7 @@
         <v>154</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="W16" s="3"/>
       <c r="X16" s="4"/>
@@ -3528,7 +3528,7 @@
         <v>519</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="W17" s="3"/>
       <c r="X17" s="4"/>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AC20" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AD20" s="32"/>
     </row>
@@ -3600,19 +3600,19 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="AC21" s="42" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AD21" s="32"/>
       <c r="AE21" s="22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AF21" s="22" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="22" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -3623,15 +3623,15 @@
         <v>5</v>
       </c>
       <c r="AE22" s="22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AF22" s="22" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="23" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -3642,73 +3642,73 @@
         <v>390</v>
       </c>
       <c r="AE23" s="22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AF23" s="22" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="24" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="AC24" s="42" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AD24" s="32"/>
       <c r="AE24" s="22"/>
     </row>
     <row r="25" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="AC25" s="42" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AD25" s="32"/>
       <c r="AE25" s="22"/>
     </row>
     <row r="26" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="AC26" s="42"/>
       <c r="AD26" s="32" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AE26" s="22"/>
     </row>
     <row r="27" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="AC27" s="42"/>
       <c r="AD27" s="32" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AE27" s="22"/>
     </row>
     <row r="28" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="AC28" s="42"/>
       <c r="AD28" s="32"/>
       <c r="AE28" s="22" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AF28" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
@@ -3788,7 +3788,7 @@
         <v>113</v>
       </c>
       <c r="AL33" s="12" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.25">
@@ -3823,7 +3823,7 @@
         <v>478</v>
       </c>
       <c r="AJ35" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
@@ -4005,10 +4005,10 @@
         <v>69</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="W42" s="5"/>
       <c r="X42" s="5" t="s">
@@ -4065,7 +4065,7 @@
         <v>151</v>
       </c>
       <c r="AL45" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AM45" t="s">
         <v>295</v>
@@ -4141,7 +4141,7 @@
         <v>184</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I48" s="12"/>
       <c r="AP48" t="s">
@@ -4204,10 +4204,10 @@
     </row>
     <row r="53" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>600</v>
+      </c>
+      <c r="P53" t="s">
         <v>601</v>
-      </c>
-      <c r="P53" t="s">
-        <v>602</v>
       </c>
       <c r="R53" s="5"/>
     </row>
@@ -4275,7 +4275,7 @@
         <v>500</v>
       </c>
       <c r="AP57" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58" spans="1:48" x14ac:dyDescent="0.25">
@@ -4348,7 +4348,7 @@
         <v>430</v>
       </c>
       <c r="P62" s="27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="63" spans="1:48" x14ac:dyDescent="0.25">
@@ -4356,7 +4356,7 @@
         <v>431</v>
       </c>
       <c r="P63" s="26" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AU63" t="s">
         <v>513</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AE64" s="33"/>
       <c r="AU64" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AV64" t="s">
         <v>315</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="R65" s="33"/>
       <c r="S65" s="33"/>
@@ -4413,7 +4413,7 @@
       <c r="AD65" s="33"/>
       <c r="AE65" s="33"/>
       <c r="AU65" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AV65" t="s">
         <v>315</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="R66" s="33"/>
       <c r="S66" s="33"/>
@@ -4438,15 +4438,15 @@
       <c r="AD66" s="33"/>
       <c r="AE66" s="33"/>
       <c r="AU66" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AV66" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="R67" s="33"/>
       <c r="S67" s="33"/>
@@ -4463,10 +4463,10 @@
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
       <c r="AU67" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AV67" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
@@ -4495,7 +4495,7 @@
         <v>444</v>
       </c>
       <c r="P69" s="26" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
@@ -4520,7 +4520,7 @@
         <v>511</v>
       </c>
       <c r="AC72" s="42" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
@@ -4528,31 +4528,31 @@
         <v>515</v>
       </c>
       <c r="P73" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="74" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P74" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="P75" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="76" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="P76" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -4748,7 +4748,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>29</v>
@@ -5057,10 +5057,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
@@ -5075,10 +5075,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" t="s">
@@ -5104,10 +5104,10 @@
         <v>192</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>29</v>
@@ -5122,10 +5122,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" t="s">
@@ -5154,10 +5154,10 @@
         <v>194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>29</v>
@@ -5172,10 +5172,10 @@
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" t="s">
@@ -5338,7 +5338,7 @@
         <v>50</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="I14" s="2"/>
       <c r="K14" t="s">
@@ -6261,7 +6261,7 @@
         <v>436</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>29</v>
@@ -6284,7 +6284,7 @@
         <v>514</v>
       </c>
       <c r="G3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -6333,7 +6333,7 @@
         <v>496</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D2" s="9"/>
       <c r="F2" s="2"/>
@@ -6434,10 +6434,10 @@
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
+        <v>613</v>
+      </c>
+      <c r="C2" t="s">
         <v>614</v>
-      </c>
-      <c r="C2" t="s">
-        <v>615</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -6531,7 +6531,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="30"/>
       <c r="K5" s="20" t="s">
-        <v>572</v>
+        <v>703</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -6559,7 +6559,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="40" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -6579,7 +6579,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -6593,7 +6593,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -6620,7 +6620,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>618</v>
+        <v>704</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -6663,12 +6663,12 @@
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -6903,18 +6903,18 @@
         <v>315</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C22" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -7014,10 +7014,10 @@
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -7082,7 +7082,7 @@
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="22" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -7111,7 +7111,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="30"/>
       <c r="K5" s="20" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -7139,7 +7139,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="22" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -7159,7 +7159,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -7173,7 +7173,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -7200,7 +7200,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -7243,12 +7243,12 @@
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="22" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -7480,21 +7480,21 @@
         <v>510</v>
       </c>
       <c r="C21" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C22" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -7594,10 +7594,10 @@
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -7662,7 +7662,7 @@
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -7691,7 +7691,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="30"/>
       <c r="K5" s="20" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -7719,7 +7719,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="40" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -7739,7 +7739,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -7753,7 +7753,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -7780,7 +7780,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -7812,7 +7812,7 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="19" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
@@ -7823,12 +7823,12 @@
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -8060,21 +8060,21 @@
         <v>510</v>
       </c>
       <c r="C21" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C22" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -8174,10 +8174,10 @@
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -8242,7 +8242,7 @@
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -8271,7 +8271,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="47"/>
       <c r="K5" s="20" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -8299,7 +8299,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="40" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -8319,7 +8319,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -8333,7 +8333,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -8360,7 +8360,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -8392,7 +8392,7 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="19" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -8643,18 +8643,18 @@
         <v>315</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C22" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -8766,15 +8766,15 @@
         <v>2</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -11057,7 +11057,7 @@
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
       <c r="U3" s="20" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="V3" s="20">
         <v>2</v>
@@ -11632,10 +11632,10 @@
       <c r="AH11" s="20"/>
       <c r="AI11" s="20"/>
       <c r="AJ11" s="45" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AK11" s="20" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AL11" s="46" t="s">
         <v>15</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -12737,7 +12737,7 @@
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
       <c r="T5" s="20" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="U5" s="20"/>
       <c r="V5" s="20"/>
@@ -12924,7 +12924,7 @@
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
@@ -13139,7 +13139,7 @@
         <v>478</v>
       </c>
       <c r="AB15" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AC15" s="20"/>
       <c r="AD15" s="20"/>
@@ -13970,7 +13970,7 @@
         <v>246</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -14001,7 +14001,7 @@
         <v>243</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C2" s="20"/>
     </row>
@@ -14011,10 +14011,10 @@
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -14032,88 +14032,88 @@
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B8" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B9" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="B12" t="s">
         <v>689</v>
-      </c>
-      <c r="B12" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="B14" t="s">
         <v>688</v>
-      </c>
-      <c r="B14" t="s">
-        <v>690</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
+++ b/src/test/resources/TestData/Hydroflask_EMEA/GoldHydroEMEA_TestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C07D09-9C6D-4E30-943C-E400EDC6218F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEE5268-F886-40A4-9B73-F1CA2757C78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataSet" sheetId="1" r:id="rId1"/>
@@ -1368,9 +1368,6 @@
     <t>Video Product_Prod</t>
   </si>
   <si>
-    <t>Wide Mouth Flex Straw Cap</t>
-  </si>
-  <si>
     <t>https://mcloud-na-preprod.hydroflask.com/shop/bottles-drinkware/bottles</t>
   </si>
   <si>
@@ -2181,14 +2178,17 @@
   <si>
     <t>Our Story,FAQ,Contact,Refill For Good,Blog</t>
   </si>
+  <si>
+    <t>Camp Bowl</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="164" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="0;[Red]0"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -2386,7 +2386,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
@@ -2412,7 +2412,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2734,30 +2734,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW76"/>
-  <sheetFormatPr defaultColWidth="56.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="56.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="30.7109375" customWidth="1"/>
-    <col min="10" max="18" width="30.5703125" customWidth="1"/>
-    <col min="19" max="19" width="19.7109375" customWidth="1"/>
-    <col min="20" max="21" width="22.28515625" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="30.6640625" customWidth="1"/>
+    <col min="10" max="18" width="30.5546875" customWidth="1"/>
+    <col min="19" max="19" width="19.6640625" customWidth="1"/>
+    <col min="20" max="21" width="22.33203125" customWidth="1"/>
+    <col min="22" max="22" width="14.6640625" customWidth="1"/>
+    <col min="23" max="23" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="9" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" customWidth="1"/>
+    <col min="28" max="28" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>165</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>312</v>
@@ -2897,7 +2897,7 @@
         <v>207</v>
       </c>
       <c r="AU1" s="39" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AV1" s="1" t="s">
         <v>433</v>
@@ -2906,15 +2906,15 @@
         <v>355</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
@@ -2929,10 +2929,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -2944,16 +2944,16 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" t="s">
+        <v>504</v>
+      </c>
+      <c r="T2" t="s">
+        <v>502</v>
+      </c>
+      <c r="V2" t="s">
         <v>505</v>
       </c>
-      <c r="T2" t="s">
-        <v>503</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="W2" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="X2" s="5" t="s">
         <v>59</v>
@@ -2961,18 +2961,18 @@
       <c r="Z2" s="5"/>
       <c r="AA2" s="7"/>
       <c r="AW2" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>293</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>29</v>
@@ -2987,10 +2987,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -3002,19 +3002,19 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
       <c r="S3" t="s">
+        <v>491</v>
+      </c>
+      <c r="T3" t="s">
+        <v>493</v>
+      </c>
+      <c r="U3" t="s">
+        <v>484</v>
+      </c>
+      <c r="V3" t="s">
         <v>492</v>
       </c>
-      <c r="T3" t="s">
+      <c r="W3" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="U3" t="s">
-        <v>485</v>
-      </c>
-      <c r="V3" t="s">
-        <v>493</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="X3" s="5" t="s">
         <v>59</v>
@@ -3022,15 +3022,15 @@
       <c r="Z3" s="5"/>
       <c r="AA3" s="7"/>
     </row>
-    <row r="4" spans="1:49" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>29</v>
@@ -3045,10 +3045,10 @@
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -3060,16 +3060,16 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="T4" t="s">
         <v>502</v>
       </c>
-      <c r="T4" t="s">
+      <c r="V4" t="s">
+        <v>480</v>
+      </c>
+      <c r="W4" t="s">
         <v>503</v>
-      </c>
-      <c r="V4" t="s">
-        <v>481</v>
-      </c>
-      <c r="W4" t="s">
-        <v>504</v>
       </c>
       <c r="X4" s="5" t="s">
         <v>59</v>
@@ -3077,15 +3077,15 @@
       <c r="Z4" s="5"/>
       <c r="AA4" s="7"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>358</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>29</v>
@@ -3100,10 +3100,10 @@
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3119,7 +3119,7 @@
       <c r="Z5" s="5"/>
       <c r="AA5" s="7"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>435</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>436</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>29</v>
@@ -3145,7 +3145,7 @@
         <v>436</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -3157,19 +3157,19 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" t="s">
+        <v>491</v>
+      </c>
+      <c r="T6" t="s">
+        <v>493</v>
+      </c>
+      <c r="U6" t="s">
+        <v>484</v>
+      </c>
+      <c r="V6" t="s">
         <v>492</v>
       </c>
-      <c r="T6" t="s">
+      <c r="W6" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="U6" t="s">
-        <v>485</v>
-      </c>
-      <c r="V6" t="s">
-        <v>493</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="X6" s="5" t="s">
         <v>59</v>
@@ -3177,15 +3177,15 @@
       <c r="Z6" s="5"/>
       <c r="AA6" s="7"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>29</v>
@@ -3200,10 +3200,10 @@
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -3215,16 +3215,16 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" t="s">
+        <v>520</v>
+      </c>
+      <c r="T7" t="s">
         <v>521</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>522</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" s="5" t="s">
         <v>523</v>
-      </c>
-      <c r="W7" s="5" t="s">
-        <v>524</v>
       </c>
       <c r="X7" s="5" t="s">
         <v>59</v>
@@ -3232,15 +3232,15 @@
       <c r="Z7" s="5"/>
       <c r="AA7" s="7"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>29</v>
@@ -3255,10 +3255,10 @@
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -3270,17 +3270,17 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="T8" s="20" t="s">
         <v>521</v>
-      </c>
-      <c r="T8" s="20" t="s">
-        <v>522</v>
       </c>
       <c r="U8" s="20"/>
       <c r="V8" s="41" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="W8" s="40" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X8" s="40" t="s">
         <v>59</v>
@@ -3289,15 +3289,15 @@
       <c r="Z8" s="5"/>
       <c r="AA8" s="7"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>29</v>
@@ -3312,10 +3312,10 @@
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -3327,17 +3327,17 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="T9" s="40" t="s">
         <v>528</v>
-      </c>
-      <c r="T9" s="40" t="s">
-        <v>529</v>
       </c>
       <c r="U9" s="20"/>
       <c r="V9" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="W9" s="40" t="s">
         <v>529</v>
-      </c>
-      <c r="W9" s="40" t="s">
-        <v>530</v>
       </c>
       <c r="X9" s="40" t="s">
         <v>59</v>
@@ -3346,15 +3346,15 @@
       <c r="Z9" s="5"/>
       <c r="AA9" s="7"/>
     </row>
-    <row r="10" spans="1:49" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>29</v>
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -3384,17 +3384,17 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="T10" s="40" t="s">
         <v>532</v>
-      </c>
-      <c r="T10" s="40" t="s">
-        <v>533</v>
       </c>
       <c r="U10" s="20"/>
       <c r="V10" s="41" t="s">
+        <v>533</v>
+      </c>
+      <c r="W10" s="40" t="s">
         <v>534</v>
-      </c>
-      <c r="W10" s="40" t="s">
-        <v>535</v>
       </c>
       <c r="X10" s="40">
         <v>9898989898</v>
@@ -3403,7 +3403,7 @@
       <c r="Z10" s="5"/>
       <c r="AA10" s="7"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>199</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -3454,10 +3454,10 @@
         <v>64</v>
       </c>
       <c r="P13" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="Q13" s="5" t="s">
         <v>579</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>580</v>
       </c>
       <c r="T13" t="s">
         <v>332</v>
@@ -3466,10 +3466,10 @@
         <v>64</v>
       </c>
       <c r="V13" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="W13" s="5" t="s">
         <v>579</v>
-      </c>
-      <c r="W13" s="5" t="s">
-        <v>580</v>
       </c>
       <c r="Z13" s="5" t="s">
         <v>297</v>
@@ -3481,7 +3481,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>296</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -3512,23 +3512,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>154</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="W16" s="3"/>
       <c r="X16" s="4"/>
       <c r="AD16" s="32"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="W17" s="3"/>
       <c r="X17" s="4"/>
@@ -3545,7 +3545,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>172</v>
       </c>
@@ -3558,21 +3558,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>170</v>
       </c>
       <c r="AC19" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AD19" s="32">
         <v>1</v>
       </c>
       <c r="AE19" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AF19" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG19" t="s">
         <v>190</v>
@@ -3584,134 +3584,134 @@
         <v>356</v>
       </c>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AC20" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AD20" s="32"/>
     </row>
-    <row r="21" spans="1:49" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="60" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="AC21" s="42" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AD21" s="32"/>
       <c r="AE21" s="22" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AF21" s="22" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" ht="60" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" ht="60" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="AC22" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AD22" s="32">
         <v>5</v>
       </c>
       <c r="AE22" s="22" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AF22" s="22" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="23" spans="1:49" ht="60" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" ht="60" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="AC23" s="42" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AD23" s="32" t="s">
         <v>390</v>
       </c>
       <c r="AE23" s="22" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AF23" s="22" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="24" spans="1:49" ht="30" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" ht="30" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="AC24" s="42" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AD24" s="32"/>
       <c r="AE24" s="22"/>
     </row>
-    <row r="25" spans="1:49" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" ht="30" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="AC25" s="42" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AD25" s="32"/>
       <c r="AE25" s="22"/>
     </row>
-    <row r="26" spans="1:49" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" ht="30" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="AC26" s="42"/>
       <c r="AD26" s="32" t="s">
+        <v>595</v>
+      </c>
+      <c r="AE26" s="22"/>
+    </row>
+    <row r="27" spans="1:49" ht="30" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>596</v>
-      </c>
-      <c r="AE26" s="22"/>
-    </row>
-    <row r="27" spans="1:49" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>597</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="AC27" s="42"/>
       <c r="AD27" s="32" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AE27" s="22"/>
     </row>
-    <row r="28" spans="1:49" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" ht="30" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="AC28" s="42"/>
       <c r="AD28" s="32"/>
       <c r="AE28" s="22" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AF28" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>440</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>176</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>175</v>
       </c>
@@ -3754,17 +3754,17 @@
         <v>259</v>
       </c>
     </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>189</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="AL32" s="12" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -3788,10 +3788,10 @@
         <v>113</v>
       </c>
       <c r="AL33" s="12" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -3820,13 +3820,13 @@
         <v>123</v>
       </c>
       <c r="AI35" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AJ35" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -3933,24 +3933,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>55</v>
       </c>
       <c r="S40" t="s">
+        <v>491</v>
+      </c>
+      <c r="T40" t="s">
+        <v>493</v>
+      </c>
+      <c r="U40" t="s">
+        <v>484</v>
+      </c>
+      <c r="V40" t="s">
         <v>492</v>
       </c>
-      <c r="T40" t="s">
+      <c r="W40" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="U40" t="s">
-        <v>485</v>
-      </c>
-      <c r="V40" t="s">
-        <v>493</v>
-      </c>
-      <c r="W40" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="X40" s="5" t="s">
         <v>59</v>
@@ -3965,7 +3965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -3976,25 +3976,25 @@
         <v>15</v>
       </c>
       <c r="S41" t="s">
+        <v>491</v>
+      </c>
+      <c r="T41" t="s">
+        <v>493</v>
+      </c>
+      <c r="U41" t="s">
+        <v>484</v>
+      </c>
+      <c r="V41" t="s">
         <v>492</v>
       </c>
-      <c r="T41" t="s">
+      <c r="W41" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="U41" t="s">
-        <v>485</v>
-      </c>
-      <c r="V41" t="s">
-        <v>493</v>
-      </c>
-      <c r="W41" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="X41" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -4005,48 +4005,48 @@
         <v>69</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="W42" s="5"/>
       <c r="X42" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>77</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E43" s="2"/>
       <c r="H43" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I43" s="2"/>
       <c r="S43" t="s">
+        <v>491</v>
+      </c>
+      <c r="T43" t="s">
+        <v>493</v>
+      </c>
+      <c r="U43" t="s">
+        <v>484</v>
+      </c>
+      <c r="V43" t="s">
         <v>492</v>
       </c>
-      <c r="T43" t="s">
+      <c r="W43" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="U43" t="s">
-        <v>485</v>
-      </c>
-      <c r="V43" t="s">
-        <v>493</v>
-      </c>
-      <c r="W43" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="X43" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>118</v>
       </c>
@@ -4060,12 +4060,12 @@
         <v>434</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>151</v>
       </c>
       <c r="AL45" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AM45" t="s">
         <v>295</v>
@@ -4077,25 +4077,25 @@
         <v>313</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>164</v>
       </c>
       <c r="R46" s="12"/>
       <c r="S46" t="s">
+        <v>491</v>
+      </c>
+      <c r="T46" t="s">
+        <v>493</v>
+      </c>
+      <c r="U46" t="s">
+        <v>484</v>
+      </c>
+      <c r="V46" t="s">
         <v>492</v>
       </c>
-      <c r="T46" t="s">
+      <c r="W46" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="U46" t="s">
-        <v>485</v>
-      </c>
-      <c r="V46" t="s">
-        <v>493</v>
-      </c>
-      <c r="W46" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="X46" s="5" t="s">
         <v>59</v>
@@ -4110,7 +4110,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>166</v>
       </c>
@@ -4136,19 +4136,19 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>184</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I48" s="12"/>
       <c r="AP48" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>278</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>283</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -4196,22 +4196,22 @@
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>209</v>
       </c>
       <c r="R52" s="5"/>
     </row>
-    <row r="53" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>599</v>
+      </c>
+      <c r="P53" t="s">
         <v>600</v>
       </c>
-      <c r="P53" t="s">
-        <v>601</v>
-      </c>
       <c r="R53" s="5"/>
     </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>338</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>340</v>
       </c>
       <c r="P54" s="26" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Q54" s="5" t="s">
         <v>354</v>
@@ -4236,7 +4236,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>342</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>345</v>
       </c>
@@ -4252,16 +4252,16 @@
         <v>428</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N56" s="24" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AP56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="57" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>347</v>
       </c>
@@ -4272,55 +4272,55 @@
         <v>348</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AP57" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="58" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>352</v>
       </c>
       <c r="P58" s="26" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="59" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>568</v>
+      </c>
+      <c r="P59" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="P59" s="26" t="s">
-        <v>570</v>
-      </c>
       <c r="S59" t="s">
+        <v>491</v>
+      </c>
+      <c r="T59" t="s">
+        <v>493</v>
+      </c>
+      <c r="U59" t="s">
+        <v>484</v>
+      </c>
+      <c r="V59" t="s">
         <v>492</v>
       </c>
-      <c r="T59" t="s">
+      <c r="W59" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="U59" t="s">
-        <v>485</v>
-      </c>
-      <c r="V59" t="s">
-        <v>493</v>
-      </c>
-      <c r="W59" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="X59" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>201</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>29</v>
@@ -4335,37 +4335,37 @@
         <v>304</v>
       </c>
     </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>362</v>
       </c>
       <c r="P61" s="26" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="62" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>430</v>
       </c>
       <c r="P62" s="27" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="63" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>431</v>
       </c>
       <c r="P63" s="26" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AU63" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AV63" s="31" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>232</v>
       </c>
@@ -4388,15 +4388,15 @@
       </c>
       <c r="AE64" s="33"/>
       <c r="AU64" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AV64" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="65" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="R65" s="33"/>
       <c r="S65" s="33"/>
@@ -4413,15 +4413,15 @@
       <c r="AD65" s="33"/>
       <c r="AE65" s="33"/>
       <c r="AU65" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AV65" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="66" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="R66" s="33"/>
       <c r="S66" s="33"/>
@@ -4438,15 +4438,15 @@
       <c r="AD66" s="33"/>
       <c r="AE66" s="33"/>
       <c r="AU66" t="s">
+        <v>636</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="67" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>637</v>
-      </c>
-      <c r="AV66" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>638</v>
       </c>
       <c r="R67" s="33"/>
       <c r="S67" s="33"/>
@@ -4463,13 +4463,13 @@
       <c r="AD67" s="33"/>
       <c r="AE67" s="33"/>
       <c r="AU67" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AV67" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="68" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A68" s="33" t="s">
         <v>153</v>
       </c>
@@ -4490,69 +4490,69 @@
       <c r="P68" s="33"/>
       <c r="Q68" s="33"/>
     </row>
-    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P69" s="26" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="70" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>498</v>
+      </c>
+      <c r="P70" s="26" t="s">
+        <v>567</v>
+      </c>
+      <c r="S70" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="71" spans="1:48" ht="30" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>507</v>
+      </c>
+      <c r="AC71" s="42"/>
+    </row>
+    <row r="72" spans="1:48" ht="30" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>510</v>
+      </c>
+      <c r="AC72" s="42" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="73" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>514</v>
+      </c>
+      <c r="P73" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>499</v>
-      </c>
-      <c r="P70" s="26" t="s">
-        <v>568</v>
-      </c>
-      <c r="S70" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="71" spans="1:48" ht="30" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>508</v>
-      </c>
-      <c r="AC71" s="42"/>
-    </row>
-    <row r="72" spans="1:48" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>511</v>
-      </c>
-      <c r="AC72" s="42" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>515</v>
-      </c>
-      <c r="P73" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="P74" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="75" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>698</v>
+      </c>
+      <c r="P75" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="76" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>699</v>
       </c>
-      <c r="P75" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="P76" t="s">
         <v>700</v>
-      </c>
-      <c r="P76" t="s">
-        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -4630,37 +4630,37 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424970FD-0802-41D9-95B0-A7EEAE48FFD7}">
   <dimension ref="A1:AA11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4743,12 +4743,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>29</v>
@@ -4763,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" t="s">
@@ -4784,7 +4784,7 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>155</v>
       </c>
@@ -4812,7 +4812,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>77</v>
       </c>
@@ -4902,7 +4902,7 @@
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -4943,18 +4943,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF1A3C9-3346-4B2E-B0CF-4F0FFA0F798B}">
   <dimension ref="A1:AF18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5052,15 +5052,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
@@ -5075,10 +5075,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" t="s">
@@ -5099,15 +5099,15 @@
       <c r="R2" s="5"/>
       <c r="S2" s="7"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>192</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>29</v>
@@ -5122,10 +5122,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" t="s">
@@ -5149,15 +5149,15 @@
       <c r="R3" s="5"/>
       <c r="S3" s="7"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>29</v>
@@ -5172,10 +5172,10 @@
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" t="s">
@@ -5196,7 +5196,7 @@
       <c r="R4" s="5"/>
       <c r="S4" s="7"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>155</v>
       </c>
@@ -5224,7 +5224,7 @@
       <c r="R6" s="5"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>154</v>
       </c>
@@ -5235,7 +5235,7 @@
       <c r="P7" s="4"/>
       <c r="V7" s="5"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>50</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I14" s="2"/>
       <c r="K14" t="s">
@@ -5372,7 +5372,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -5424,7 +5424,7 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -5477,12 +5477,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41F8855-2B61-4FEF-9344-24F4972CEB0C}">
   <dimension ref="A1:W6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="20" max="20" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5553,15 +5553,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>29</v>
@@ -5576,10 +5576,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" t="s">
@@ -5600,7 +5600,7 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="7"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -5616,15 +5616,15 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>187</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>29</v>
@@ -5647,7 +5647,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>154</v>
       </c>
@@ -5683,20 +5683,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29915A7A-9757-4FAB-8D6E-89B484B75E0F}">
   <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" customWidth="1"/>
-    <col min="21" max="21" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="15.28515625" customWidth="1"/>
-    <col min="27" max="27" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" customWidth="1"/>
+    <col min="21" max="21" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="15.33203125" customWidth="1"/>
+    <col min="27" max="27" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5785,15 +5785,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
@@ -5808,10 +5808,10 @@
         <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" t="s">
@@ -5833,7 +5833,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="7"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -5849,7 +5849,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>215</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>221</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>155</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>154</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>224</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>209</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>210</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>226</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>217</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>153</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>187</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>168</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>166</v>
       </c>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="Q22" s="5"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -6215,19 +6215,19 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EEBDD4E-15C0-4517-B53D-FC4E89764F23}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="158.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="158.7109375" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="158.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="158.6640625" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>436</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>29</v>
@@ -6276,15 +6276,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>199</v>
       </c>
       <c r="F3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -6302,16 +6302,16 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F808DC-2462-40F4-8FE6-41754E94FF50}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="102.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="102.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -6325,15 +6325,15 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>152</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D2" s="9"/>
       <c r="F2" s="2"/>
@@ -6346,28 +6346,28 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEAA7450-0FE7-4C50-95DC-266117BAF81B}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.85546875" customWidth="1"/>
-    <col min="4" max="4" width="62.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.88671875" customWidth="1"/>
+    <col min="4" max="4" width="62.88671875" customWidth="1"/>
     <col min="5" max="5" width="78" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="78" customWidth="1"/>
     <col min="7" max="7" width="84" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="77.5703125" customWidth="1"/>
-    <col min="10" max="10" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="55.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="55.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="77.5546875" customWidth="1"/>
+    <col min="10" max="10" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="69.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.140625" customWidth="1"/>
+    <col min="15" max="15" width="59.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.109375" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
@@ -6429,15 +6429,15 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="C2" t="s">
         <v>613</v>
-      </c>
-      <c r="C2" t="s">
-        <v>614</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -6457,7 +6457,7 @@
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>230</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>264</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>275</v>
@@ -6487,13 +6487,13 @@
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -6502,7 +6502,7 @@
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -6515,7 +6515,7 @@
       <c r="S4" s="20"/>
       <c r="T4" s="20"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>233</v>
       </c>
@@ -6531,7 +6531,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="30"/>
       <c r="K5" s="20" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -6543,7 +6543,7 @@
       <c r="S5" s="20"/>
       <c r="T5" s="20"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>236</v>
       </c>
@@ -6559,7 +6559,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="40" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -6577,9 +6577,9 @@
       <c r="S6" s="20"/>
       <c r="T6" s="20"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -6593,7 +6593,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -6603,7 +6603,7 @@
       <c r="S7" s="20"/>
       <c r="T7" s="20"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>238</v>
       </c>
@@ -6620,7 +6620,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -6629,13 +6629,13 @@
       <c r="S8" s="20"/>
       <c r="T8" s="20"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>261</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -6652,23 +6652,23 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="19" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>280</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -6685,7 +6685,7 @@
       <c r="S10" s="20"/>
       <c r="T10" s="20"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>285</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>317</v>
       </c>
@@ -6739,7 +6739,7 @@
       <c r="S12" s="20"/>
       <c r="T12" s="20"/>
     </row>
-    <row r="13" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>319</v>
       </c>
@@ -6750,10 +6750,10 @@
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="34" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
@@ -6767,7 +6767,7 @@
       <c r="S13" s="20"/>
       <c r="T13" s="20"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>320</v>
       </c>
@@ -6793,7 +6793,7 @@
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>322</v>
       </c>
@@ -6819,14 +6819,14 @@
       <c r="S15" s="20"/>
       <c r="T15" s="20"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>333</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
@@ -6845,7 +6845,7 @@
       <c r="S16" s="20"/>
       <c r="T16" s="20"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>336</v>
       </c>
@@ -6871,50 +6871,50 @@
       <c r="S17" s="20"/>
       <c r="T17" s="20"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="D18" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="D19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="D19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="R20" t="s">
         <v>448</v>
       </c>
-      <c r="R20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C21" t="s">
         <v>315</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C22" t="s">
+        <v>616</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>617</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -6926,28 +6926,28 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9DB2F9-2571-41BC-A47E-955F00D431F8}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.85546875" customWidth="1"/>
-    <col min="4" max="4" width="62.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.88671875" customWidth="1"/>
+    <col min="4" max="4" width="62.88671875" customWidth="1"/>
     <col min="5" max="5" width="78" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="78" customWidth="1"/>
     <col min="7" max="7" width="84" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="77.5703125" customWidth="1"/>
-    <col min="10" max="10" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="55.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="55.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="77.5546875" customWidth="1"/>
+    <col min="10" max="10" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="69.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.140625" customWidth="1"/>
+    <col min="15" max="15" width="59.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.109375" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
@@ -7009,15 +7009,15 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="C2" t="s">
         <v>670</v>
-      </c>
-      <c r="C2" t="s">
-        <v>671</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -7037,7 +7037,7 @@
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>230</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>264</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>275</v>
@@ -7067,13 +7067,13 @@
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -7082,7 +7082,7 @@
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="22" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -7095,7 +7095,7 @@
       <c r="S4" s="20"/>
       <c r="T4" s="20"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>233</v>
       </c>
@@ -7111,7 +7111,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="30"/>
       <c r="K5" s="20" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -7123,7 +7123,7 @@
       <c r="S5" s="20"/>
       <c r="T5" s="20"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>236</v>
       </c>
@@ -7139,7 +7139,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="22" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -7157,9 +7157,9 @@
       <c r="S6" s="20"/>
       <c r="T6" s="20"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -7173,7 +7173,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -7183,7 +7183,7 @@
       <c r="S7" s="20"/>
       <c r="T7" s="20"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>238</v>
       </c>
@@ -7200,7 +7200,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -7209,13 +7209,13 @@
       <c r="S8" s="20"/>
       <c r="T8" s="20"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>261</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -7232,23 +7232,23 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="19" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>280</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="22" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -7265,7 +7265,7 @@
       <c r="S10" s="20"/>
       <c r="T10" s="20"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>285</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>317</v>
       </c>
@@ -7319,7 +7319,7 @@
       <c r="S12" s="20"/>
       <c r="T12" s="20"/>
     </row>
-    <row r="13" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>319</v>
       </c>
@@ -7330,10 +7330,10 @@
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="34" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
@@ -7347,7 +7347,7 @@
       <c r="S13" s="20"/>
       <c r="T13" s="20"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>320</v>
       </c>
@@ -7373,7 +7373,7 @@
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>322</v>
       </c>
@@ -7399,14 +7399,14 @@
       <c r="S15" s="20"/>
       <c r="T15" s="20"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>333</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
@@ -7425,7 +7425,7 @@
       <c r="S16" s="20"/>
       <c r="T16" s="20"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>336</v>
       </c>
@@ -7451,50 +7451,50 @@
       <c r="S17" s="20"/>
       <c r="T17" s="20"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="D18" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="D19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="D19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="R20" t="s">
         <v>448</v>
       </c>
-      <c r="R20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C21" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K21" s="5" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>572</v>
+      </c>
+      <c r="C22" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="K22" s="5" t="s">
         <v>680</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -7506,28 +7506,28 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B30F424-6152-48B1-B4CB-73BD0DB11C04}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.85546875" customWidth="1"/>
-    <col min="4" max="4" width="62.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.88671875" customWidth="1"/>
+    <col min="4" max="4" width="62.88671875" customWidth="1"/>
     <col min="5" max="5" width="78" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="78" customWidth="1"/>
     <col min="7" max="7" width="84" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="77.5703125" customWidth="1"/>
-    <col min="10" max="10" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="55.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="55.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="77.5546875" customWidth="1"/>
+    <col min="10" max="10" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="69.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.140625" customWidth="1"/>
+    <col min="15" max="15" width="59.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.109375" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
@@ -7589,15 +7589,15 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -7617,7 +7617,7 @@
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>230</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>264</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>275</v>
@@ -7647,13 +7647,13 @@
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -7662,7 +7662,7 @@
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -7675,7 +7675,7 @@
       <c r="S4" s="20"/>
       <c r="T4" s="20"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>233</v>
       </c>
@@ -7691,7 +7691,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="30"/>
       <c r="K5" s="20" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -7703,7 +7703,7 @@
       <c r="S5" s="20"/>
       <c r="T5" s="20"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>236</v>
       </c>
@@ -7719,7 +7719,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="40" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -7737,9 +7737,9 @@
       <c r="S6" s="20"/>
       <c r="T6" s="20"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -7753,7 +7753,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -7763,7 +7763,7 @@
       <c r="S7" s="20"/>
       <c r="T7" s="20"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>238</v>
       </c>
@@ -7780,7 +7780,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -7789,13 +7789,13 @@
       <c r="S8" s="20"/>
       <c r="T8" s="20"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>261</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -7812,23 +7812,23 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="19" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>280</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -7845,7 +7845,7 @@
       <c r="S10" s="20"/>
       <c r="T10" s="20"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>285</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>317</v>
       </c>
@@ -7899,7 +7899,7 @@
       <c r="S12" s="20"/>
       <c r="T12" s="20"/>
     </row>
-    <row r="13" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>319</v>
       </c>
@@ -7910,10 +7910,10 @@
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="34" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
@@ -7927,7 +7927,7 @@
       <c r="S13" s="20"/>
       <c r="T13" s="20"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>320</v>
       </c>
@@ -7953,7 +7953,7 @@
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>322</v>
       </c>
@@ -7979,14 +7979,14 @@
       <c r="S15" s="20"/>
       <c r="T15" s="20"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>333</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
@@ -8005,7 +8005,7 @@
       <c r="S16" s="20"/>
       <c r="T16" s="20"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>336</v>
       </c>
@@ -8031,50 +8031,50 @@
       <c r="S17" s="20"/>
       <c r="T17" s="20"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="D18" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="D19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="D19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="R20" t="s">
         <v>448</v>
       </c>
-      <c r="R20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C21" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K21" s="5" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>572</v>
+      </c>
+      <c r="C22" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="C22" t="s">
-        <v>652</v>
-      </c>
       <c r="K22" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -8085,29 +8085,29 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5618368D-AD25-46EB-B468-A08A28DAB485}">
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="70.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="117.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="51.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="117.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="56.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="78" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="100.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="100.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="79" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="92.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="83.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="92.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="83.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="59.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
@@ -8169,15 +8169,15 @@
         <v>432</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
@@ -8197,7 +8197,7 @@
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>230</v>
       </c>
@@ -8208,7 +8208,7 @@
         <v>264</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>275</v>
@@ -8227,13 +8227,13 @@
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
@@ -8242,7 +8242,7 @@
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
@@ -8255,7 +8255,7 @@
       <c r="S4" s="20"/>
       <c r="T4" s="20"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>233</v>
       </c>
@@ -8271,7 +8271,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="47"/>
       <c r="K5" s="20" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -8283,7 +8283,7 @@
       <c r="S5" s="20"/>
       <c r="T5" s="20"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>236</v>
       </c>
@@ -8299,7 +8299,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
       <c r="M6" s="40" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="19" t="s">
@@ -8317,9 +8317,9 @@
       <c r="S6" s="20"/>
       <c r="T6" s="20"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -8333,7 +8333,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="40" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="19"/>
@@ -8343,7 +8343,7 @@
       <c r="S7" s="20"/>
       <c r="T7" s="20"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>238</v>
       </c>
@@ -8360,7 +8360,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="28" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -8369,13 +8369,13 @@
       <c r="S8" s="20"/>
       <c r="T8" s="20"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>261</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -8392,23 +8392,23 @@
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="19" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>280</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
@@ -8425,7 +8425,7 @@
       <c r="S10" s="20"/>
       <c r="T10" s="20"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>285</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>317</v>
       </c>
@@ -8479,7 +8479,7 @@
       <c r="S12" s="20"/>
       <c r="T12" s="20"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>319</v>
       </c>
@@ -8490,10 +8490,10 @@
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="28" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
@@ -8507,7 +8507,7 @@
       <c r="S13" s="20"/>
       <c r="T13" s="20"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>320</v>
       </c>
@@ -8533,7 +8533,7 @@
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>322</v>
       </c>
@@ -8559,14 +8559,14 @@
       <c r="S15" s="20"/>
       <c r="T15" s="20"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>333</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
@@ -8585,7 +8585,7 @@
       <c r="S16" s="20"/>
       <c r="T16" s="20"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>336</v>
       </c>
@@ -8611,50 +8611,50 @@
       <c r="S17" s="20"/>
       <c r="T17" s="20"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="D18" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="D19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="D19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="R20" t="s">
         <v>448</v>
       </c>
-      <c r="R20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C21" t="s">
         <v>315</v>
       </c>
       <c r="K21" s="5" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>572</v>
+      </c>
+      <c r="C22" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="K22" s="5" t="s">
         <v>666</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -8665,18 +8665,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66895830-5267-4F1F-BE18-CA2A151CA6D1}">
   <dimension ref="A1:AF6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -8709,12 +8709,12 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>561</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>562</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -8727,27 +8727,27 @@
       <c r="R2" s="5"/>
       <c r="S2" s="7"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B3" s="12"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="R3" s="5"/>
       <c r="S3" s="7"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="H4" s="9"/>
       <c r="R4" s="5"/>
       <c r="S4" s="7"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="H5" s="12"/>
       <c r="O5" s="3"/>
       <c r="P5" s="4"/>
       <c r="V5" s="5"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="H6" s="5"/>
     </row>
   </sheetData>
@@ -8759,22 +8759,22 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A11CD39-B43D-4ECF-B59A-D818AB33DAB7}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B2" t="s">
         <v>592</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>591</v>
-      </c>
-      <c r="B2" t="s">
-        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -8785,31 +8785,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4579BB67-5E19-4DC2-AEAD-551C7DC854EB}">
   <dimension ref="A1:AX71"/>
-  <sheetFormatPr defaultColWidth="56.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="56.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="17.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="30.7109375" customWidth="1"/>
-    <col min="17" max="24" width="30.5703125" customWidth="1"/>
-    <col min="25" max="25" width="19.7109375" customWidth="1"/>
-    <col min="26" max="27" width="22.28515625" customWidth="1"/>
-    <col min="28" max="28" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="17.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="30.6640625" customWidth="1"/>
+    <col min="17" max="24" width="30.5546875" customWidth="1"/>
+    <col min="25" max="25" width="19.6640625" customWidth="1"/>
+    <col min="26" max="27" width="22.33203125" customWidth="1"/>
+    <col min="28" max="28" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="9" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="14" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" customWidth="1"/>
+    <col min="34" max="34" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -9031,12 +9031,12 @@
       <c r="AF2" s="5"/>
       <c r="AG2" s="7"/>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>273</v>
@@ -9065,7 +9065,7 @@
         <v>425</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>273</v>
@@ -9101,12 +9101,12 @@
       <c r="AF3" s="5"/>
       <c r="AG3" s="7"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>273</v>
@@ -9135,7 +9135,7 @@
         <v>425</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>273</v>
@@ -9171,12 +9171,12 @@
       <c r="AF4" s="5"/>
       <c r="AG4" s="7"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>273</v>
@@ -9205,7 +9205,7 @@
         <v>425</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>273</v>
@@ -9241,12 +9241,12 @@
       <c r="AF5" s="5"/>
       <c r="AG5" s="7"/>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>273</v>
@@ -9275,7 +9275,7 @@
         <v>425</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>273</v>
@@ -9311,12 +9311,12 @@
       <c r="AF6" s="5"/>
       <c r="AG6" s="7"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>273</v>
@@ -9345,7 +9345,7 @@
         <v>425</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>273</v>
@@ -9381,12 +9381,12 @@
       <c r="AF7" s="5"/>
       <c r="AG7" s="7"/>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -9422,12 +9422,12 @@
       <c r="AF8" s="5"/>
       <c r="AG8" s="7"/>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -9463,12 +9463,12 @@
       <c r="AF9" s="5"/>
       <c r="AG9" s="7"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>273</v>
@@ -9497,7 +9497,7 @@
         <v>425</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>273</v>
@@ -9533,7 +9533,7 @@
       <c r="AF10" s="5"/>
       <c r="AG10" s="7"/>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>405</v>
       </c>
@@ -9594,7 +9594,7 @@
       <c r="AF11" s="5"/>
       <c r="AG11" s="7"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>293</v>
       </c>
@@ -9653,7 +9653,7 @@
       <c r="AF12" s="5"/>
       <c r="AG12" s="7"/>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>358</v>
       </c>
@@ -9699,7 +9699,7 @@
       <c r="AF13" s="5"/>
       <c r="AG13" s="7"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>296</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>155</v>
       </c>
@@ -9764,7 +9764,7 @@
       <c r="AF16" s="5"/>
       <c r="AG16" s="7"/>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>154</v>
       </c>
@@ -9775,7 +9775,7 @@
       <c r="AD17" s="4"/>
       <c r="AJ17" s="5"/>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>365</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>367</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>369</v>
       </c>
@@ -9836,7 +9836,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>396</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>375</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>377</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>379</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>400</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>404</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>381</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>384</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>410</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>411</v>
       </c>
@@ -10009,7 +10009,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>385</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>388</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>402</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>389</v>
       </c>
@@ -10064,7 +10064,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>423</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>397</v>
       </c>
@@ -10090,7 +10090,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>393</v>
       </c>
@@ -10106,7 +10106,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>422</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>394</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>401</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>414</v>
       </c>
@@ -10173,7 +10173,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="44" spans="1:41" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>224</v>
       </c>
@@ -10191,7 +10191,7 @@
       <c r="AI44" s="25"/>
       <c r="AJ44" s="5"/>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>413</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>217</v>
       </c>
@@ -10224,7 +10224,7 @@
       <c r="AI46" s="25"/>
       <c r="AJ46" s="5"/>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>176</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>175</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>189</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>43</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -10436,7 +10436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>77</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>118</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>166</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>283</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>372</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>215</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>209</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>338</v>
       </c>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>342</v>
       </c>
@@ -10634,7 +10634,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>345</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>347</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>352</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="70" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>201</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>362</v>
       </c>
@@ -10791,37 +10791,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AS18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.7109375" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.6640625" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="11" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>3</v>
       </c>
@@ -10990,16 +10990,16 @@
       </c>
       <c r="L2" s="29"/>
       <c r="M2" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="O2" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="P2" s="20" t="s">
         <v>494</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>495</v>
       </c>
       <c r="Q2" s="20">
         <v>9898989898</v>
@@ -11033,7 +11033,7 @@
       <c r="AR2" s="20"/>
       <c r="AS2" s="20"/>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>25</v>
       </c>
@@ -11057,7 +11057,7 @@
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
       <c r="U3" s="20" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="V3" s="20">
         <v>2</v>
@@ -11090,7 +11090,7 @@
       <c r="AR3" s="20"/>
       <c r="AS3" s="20"/>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>248</v>
       </c>
@@ -11143,7 +11143,7 @@
       <c r="AR4" s="20"/>
       <c r="AS4" s="20"/>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>68</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>331</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K5" s="29"/>
       <c r="L5" s="20"/>
@@ -11206,7 +11206,7 @@
       <c r="AR5" s="20"/>
       <c r="AS5" s="20"/>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>75</v>
       </c>
@@ -11231,21 +11231,21 @@
         <v>67</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K6" s="29"/>
       <c r="L6" s="20"/>
       <c r="M6" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="O6" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="P6" s="20" t="s">
         <v>494</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="P6" s="20" t="s">
-        <v>495</v>
       </c>
       <c r="Q6" s="20">
         <v>9898989898</v>
@@ -11285,12 +11285,12 @@
       <c r="AR6" s="20"/>
       <c r="AS6" s="20"/>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>81</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="20"/>
@@ -11304,23 +11304,23 @@
         <v>96</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K7" s="29"/>
       <c r="L7" s="20" t="s">
         <v>81</v>
       </c>
       <c r="M7" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="O7" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="N7" s="20" t="s">
+      <c r="P7" s="20" t="s">
         <v>494</v>
-      </c>
-      <c r="O7" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="P7" s="20" t="s">
-        <v>495</v>
       </c>
       <c r="Q7" s="20">
         <v>9898989898</v>
@@ -11374,12 +11374,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>100</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C8" s="29"/>
       <c r="D8" s="20"/>
@@ -11393,23 +11393,23 @@
         <v>96</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K8" s="29"/>
       <c r="L8" s="20" t="s">
         <v>100</v>
       </c>
       <c r="M8" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="O8" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="P8" s="20" t="s">
         <v>494</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>495</v>
       </c>
       <c r="Q8" s="20">
         <v>9898989898</v>
@@ -11457,12 +11457,12 @@
       <c r="AR8" s="20"/>
       <c r="AS8" s="20"/>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="20"/>
@@ -11476,23 +11476,23 @@
         <v>96</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K9" s="29"/>
       <c r="L9" s="20" t="s">
         <v>95</v>
       </c>
       <c r="M9" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="O9" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="N9" s="20" t="s">
+      <c r="P9" s="20" t="s">
         <v>494</v>
-      </c>
-      <c r="O9" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="P9" s="20" t="s">
-        <v>495</v>
       </c>
       <c r="Q9" s="20">
         <v>9898989898</v>
@@ -11542,7 +11542,7 @@
       <c r="AR9" s="20"/>
       <c r="AS9" s="20"/>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>40</v>
       </c>
@@ -11593,7 +11593,7 @@
       <c r="AR10" s="20"/>
       <c r="AS10" s="20"/>
     </row>
-    <row r="11" spans="1:45" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>103</v>
       </c>
@@ -11632,16 +11632,16 @@
       <c r="AH11" s="20"/>
       <c r="AI11" s="20"/>
       <c r="AJ11" s="45" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AK11" s="20" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AL11" s="46" t="s">
         <v>15</v>
       </c>
       <c r="AM11" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AN11" s="20"/>
       <c r="AO11" s="20"/>
@@ -11650,7 +11650,7 @@
       <c r="AR11" s="20"/>
       <c r="AS11" s="20"/>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>107</v>
       </c>
@@ -11667,23 +11667,23 @@
         <v>67</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>28</v>
       </c>
       <c r="L12" s="20"/>
       <c r="M12" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="N12" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="O12" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="N12" s="20" t="s">
+      <c r="P12" s="20" t="s">
         <v>494</v>
-      </c>
-      <c r="O12" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="P12" s="20" t="s">
-        <v>495</v>
       </c>
       <c r="Q12" s="20">
         <v>9898989898</v>
@@ -11725,7 +11725,7 @@
       <c r="AR12" s="20"/>
       <c r="AS12" s="20"/>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>112</v>
       </c>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K13" s="29"/>
       <c r="L13" s="20"/>
@@ -11788,7 +11788,7 @@
       <c r="AR13" s="20"/>
       <c r="AS13" s="20"/>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>249</v>
       </c>
@@ -11843,7 +11843,7 @@
       <c r="AR14" s="20"/>
       <c r="AS14" s="20"/>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>119</v>
       </c>
@@ -11900,7 +11900,7 @@
       <c r="AR15" s="20"/>
       <c r="AS15" s="20"/>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>121</v>
       </c>
@@ -11955,7 +11955,7 @@
       <c r="AR16" s="20"/>
       <c r="AS16" s="20"/>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>219</v>
       </c>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="I17" s="20"/>
       <c r="J17" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K17" s="29"/>
       <c r="L17" s="20"/>
@@ -12010,7 +12010,7 @@
       <c r="AR17" s="20"/>
       <c r="AS17" s="20"/>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>154</v>
       </c>
@@ -12095,13 +12095,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -12178,12 +12178,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="R2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S2" t="s">
         <v>260</v>
@@ -12203,25 +12203,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AG4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="4" max="4" width="60.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.85546875" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="4" max="4" width="60.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.88671875" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" customWidth="1"/>
+    <col min="32" max="32" width="14.88671875" customWidth="1"/>
     <col min="33" max="33" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -12322,7 +12322,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>127</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>156</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>161</v>
       </c>
@@ -12461,27 +12461,27 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AE34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.42578125" customWidth="1"/>
-    <col min="22" max="22" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.44140625" customWidth="1"/>
+    <col min="22" max="22" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>3</v>
       </c>
@@ -12606,16 +12606,16 @@
       </c>
       <c r="J2" s="29"/>
       <c r="K2" s="20" t="s">
+        <v>478</v>
+      </c>
+      <c r="L2" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="M2" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="N2" s="20" t="s">
         <v>481</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>482</v>
       </c>
       <c r="O2" s="20">
         <v>9898989898</v>
@@ -12637,7 +12637,7 @@
       <c r="AD2" s="20"/>
       <c r="AE2" s="20"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>20</v>
       </c>
@@ -12678,9 +12678,9 @@
       <c r="AD3" s="20"/>
       <c r="AE3" s="20"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -12700,7 +12700,7 @@
       <c r="Q4" s="40"/>
       <c r="R4" s="7"/>
       <c r="T4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="U4" s="20"/>
       <c r="V4" s="20"/>
@@ -12714,7 +12714,7 @@
       <c r="AD4" s="20"/>
       <c r="AE4" s="20"/>
     </row>
-    <row r="5" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>25</v>
       </c>
@@ -12737,7 +12737,7 @@
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
       <c r="T5" s="20" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="U5" s="20"/>
       <c r="V5" s="20"/>
@@ -12745,10 +12745,10 @@
         <v>1</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Y5" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="Z5" s="20"/>
       <c r="AA5" s="20"/>
@@ -12757,7 +12757,7 @@
       <c r="AD5" s="20"/>
       <c r="AE5" s="20"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>178</v>
       </c>
@@ -12796,7 +12796,7 @@
       <c r="AD6" s="20"/>
       <c r="AE6" s="20"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>179</v>
       </c>
@@ -12835,7 +12835,7 @@
       <c r="AD7" s="20"/>
       <c r="AE7" s="20"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>153</v>
       </c>
@@ -12874,7 +12874,7 @@
       <c r="AD8" s="20"/>
       <c r="AE8" s="20"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>155</v>
       </c>
@@ -12911,7 +12911,7 @@
       <c r="AD9" s="20"/>
       <c r="AE9" s="20"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>154</v>
       </c>
@@ -12924,7 +12924,7 @@
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
@@ -12948,7 +12948,7 @@
       <c r="AD10" s="20"/>
       <c r="AE10" s="20"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>168</v>
       </c>
@@ -12985,7 +12985,7 @@
       <c r="AD11" s="20"/>
       <c r="AE11" s="20"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>172</v>
       </c>
@@ -13028,7 +13028,7 @@
       <c r="AD12" s="20"/>
       <c r="AE12" s="20"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>170</v>
       </c>
@@ -13067,20 +13067,20 @@
       <c r="AD13" s="20"/>
       <c r="AE13" s="20"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>77</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I14" s="29"/>
       <c r="J14" s="20"/>
@@ -13106,7 +13106,7 @@
       <c r="AD14" s="20"/>
       <c r="AE14" s="20"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>43</v>
       </c>
@@ -13136,16 +13136,16 @@
       <c r="Y15" s="20"/>
       <c r="Z15" s="20"/>
       <c r="AA15" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AB15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AC15" s="20"/>
       <c r="AD15" s="20"/>
       <c r="AE15" s="20"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>118</v>
       </c>
@@ -13163,16 +13163,16 @@
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
       <c r="K16" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="L16" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="L16" s="20" t="s">
+      <c r="M16" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="M16" s="20" t="s">
+      <c r="N16" s="20" t="s">
         <v>485</v>
-      </c>
-      <c r="N16" s="20" t="s">
-        <v>486</v>
       </c>
       <c r="O16" s="20">
         <v>9898989898</v>
@@ -13194,7 +13194,7 @@
       <c r="AD16" s="20"/>
       <c r="AE16" s="20"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>44</v>
       </c>
@@ -13214,7 +13214,7 @@
       <c r="O17" s="20"/>
       <c r="P17" s="20"/>
       <c r="Q17" s="40" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="R17" s="7" t="s">
         <v>439</v>
@@ -13235,7 +13235,7 @@
       <c r="AD17" s="20"/>
       <c r="AE17" s="20"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>46</v>
       </c>
@@ -13276,7 +13276,7 @@
       <c r="AD18" s="20"/>
       <c r="AE18" s="20"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>201</v>
       </c>
@@ -13331,7 +13331,7 @@
       <c r="AD19" s="20"/>
       <c r="AE19" s="20"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
         <v>241</v>
       </c>
@@ -13368,7 +13368,7 @@
       <c r="AD20" s="20"/>
       <c r="AE20" s="20"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>187</v>
       </c>
@@ -13415,7 +13415,7 @@
       <c r="AD21" s="20"/>
       <c r="AE21" s="20"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>166</v>
       </c>
@@ -13462,7 +13462,7 @@
       <c r="AD22" s="20"/>
       <c r="AE22" s="20"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
         <v>342</v>
       </c>
@@ -13499,7 +13499,7 @@
       <c r="AD23" s="20"/>
       <c r="AE23" s="20"/>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>345</v>
       </c>
@@ -13524,7 +13524,7 @@
       <c r="T24" s="20"/>
       <c r="U24" s="20"/>
       <c r="V24" s="20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="W24" s="20"/>
       <c r="X24" s="20"/>
@@ -13536,7 +13536,7 @@
       <c r="AD24" s="20"/>
       <c r="AE24" s="20"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
         <v>347</v>
       </c>
@@ -13551,7 +13551,7 @@
         <v>348</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
@@ -13581,7 +13581,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>40</v>
       </c>
@@ -13616,15 +13616,15 @@
       <c r="AD26" s="20"/>
       <c r="AE26" s="20"/>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>29</v>
@@ -13639,37 +13639,37 @@
         <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K27" t="s">
+        <v>520</v>
+      </c>
+      <c r="L27" t="s">
         <v>521</v>
       </c>
-      <c r="L27" t="s">
+      <c r="M27" t="s">
         <v>522</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" s="5" t="s">
         <v>523</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>524</v>
       </c>
       <c r="O27" s="5" t="s">
         <v>59</v>
       </c>
       <c r="P27" s="5"/>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>29</v>
@@ -13684,37 +13684,37 @@
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K28" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="L28" s="20" t="s">
         <v>521</v>
       </c>
-      <c r="L28" s="20" t="s">
-        <v>522</v>
-      </c>
       <c r="M28" s="41" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N28" s="40" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O28" s="40" t="s">
         <v>59</v>
       </c>
       <c r="P28" s="40"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>29</v>
@@ -13729,37 +13729,37 @@
         <v>15</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K29" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="L29" s="40" t="s">
         <v>528</v>
       </c>
-      <c r="L29" s="40" t="s">
+      <c r="M29" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="N29" s="40" t="s">
         <v>529</v>
-      </c>
-      <c r="M29" s="41" t="s">
-        <v>529</v>
-      </c>
-      <c r="N29" s="40" t="s">
-        <v>530</v>
       </c>
       <c r="O29" s="40" t="s">
         <v>59</v>
       </c>
       <c r="P29" s="40"/>
     </row>
-    <row r="30" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>29</v>
@@ -13774,31 +13774,31 @@
         <v>15</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K30" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="L30" s="40" t="s">
         <v>532</v>
       </c>
-      <c r="L30" s="40" t="s">
+      <c r="M30" s="41" t="s">
         <v>533</v>
       </c>
-      <c r="M30" s="41" t="s">
+      <c r="N30" s="40" t="s">
         <v>534</v>
-      </c>
-      <c r="N30" s="40" t="s">
-        <v>535</v>
       </c>
       <c r="O30" s="40">
         <v>9898989898</v>
       </c>
       <c r="P30" s="40"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
@@ -13807,24 +13807,24 @@
         <v>15</v>
       </c>
       <c r="K31" s="43" t="s">
+        <v>538</v>
+      </c>
+      <c r="L31" s="43" t="s">
         <v>539</v>
       </c>
-      <c r="L31" s="43" t="s">
+      <c r="M31" s="43" t="s">
         <v>540</v>
       </c>
-      <c r="M31" s="43" t="s">
+      <c r="N31" s="44" t="s">
         <v>541</v>
-      </c>
-      <c r="N31" s="44" t="s">
-        <v>542</v>
       </c>
       <c r="O31">
         <v>9898989898</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
@@ -13833,24 +13833,24 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
+        <v>542</v>
+      </c>
+      <c r="L32" t="s">
         <v>543</v>
       </c>
-      <c r="L32" t="s">
+      <c r="M32" s="18" t="s">
         <v>544</v>
       </c>
-      <c r="M32" s="18" t="s">
+      <c r="N32" s="5" t="s">
         <v>545</v>
-      </c>
-      <c r="N32" s="5" t="s">
-        <v>546</v>
       </c>
       <c r="O32">
         <v>9898989898</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
@@ -13859,24 +13859,24 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
+        <v>550</v>
+      </c>
+      <c r="L33" t="s">
         <v>551</v>
       </c>
-      <c r="L33" t="s">
+      <c r="M33" t="s">
         <v>552</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="N33" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="O33">
         <v>9898989898</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -13885,16 +13885,16 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L34" t="s">
+        <v>554</v>
+      </c>
+      <c r="M34" t="s">
+        <v>556</v>
+      </c>
+      <c r="N34" s="5" t="s">
         <v>555</v>
-      </c>
-      <c r="M34" t="s">
-        <v>557</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>556</v>
       </c>
       <c r="O34">
         <v>9898989898</v>
@@ -13949,17 +13949,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF53EDC-31F8-48E9-83B2-56073048BB22}">
   <dimension ref="A1:AA14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="82.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="154.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="82.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="154.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
@@ -13970,7 +13970,7 @@
         <v>246</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -13996,124 +13996,124 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C2" s="20"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>245</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>247</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>311</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="B6" t="s">
         <v>621</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="C7" s="20" t="s">
         <v>623</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="D7" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="B8" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="B9" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="D10" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
         <v>624</v>
       </c>
-      <c r="D7" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>628</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B11" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="B12" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>684</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C13" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="D13" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>629</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>624</v>
-      </c>
-      <c r="D10" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="B11" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="B14" t="s">
         <v>687</v>
-      </c>
-      <c r="B12" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>627</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>624</v>
-      </c>
-      <c r="D13" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>686</v>
-      </c>
-      <c r="B14" t="s">
-        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -14124,20 +14124,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ACADB97-3AA8-40BF-AE7E-787123A27C76}">
   <dimension ref="A1:V7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40.88671875" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="35" customWidth="1"/>
-    <col min="22" max="22" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -14205,15 +14205,15 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>491</v>
+      <c r="B2" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>581</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
@@ -14227,8 +14227,8 @@
       <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>491</v>
+      <c r="H2" s="12" t="s">
+        <v>581</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" t="s">
@@ -14249,7 +14249,7 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="7"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -14265,25 +14265,26 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>182</v>
       </c>
+      <c r="B4" s="12"/>
       <c r="H4" s="2"/>
       <c r="S4" t="s">
-        <v>441</v>
+        <v>704</v>
       </c>
       <c r="T4" t="s">
-        <v>441</v>
+        <v>704</v>
       </c>
       <c r="U4" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="V4" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="V4" s="12" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>155</v>
       </c>
@@ -14291,7 +14292,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>154</v>
       </c>
@@ -14299,21 +14300,21 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>206</v>
       </c>
       <c r="S7" t="s">
-        <v>441</v>
+        <v>704</v>
       </c>
       <c r="T7" t="s">
-        <v>441</v>
+        <v>704</v>
       </c>
       <c r="U7" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>490</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -14322,7 +14323,9 @@
     <hyperlink ref="D2" r:id="rId2" xr:uid="{9E532A61-7689-4A4A-898C-BE7E9CB6215A}"/>
     <hyperlink ref="V4" r:id="rId3" xr:uid="{EA733312-6E6E-4953-8ABD-93D9E78E2DFC}"/>
     <hyperlink ref="V7" r:id="rId4" xr:uid="{E7C00755-F92C-460C-AD6C-18F45A7CA941}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{EC234BB6-B8A0-428F-A79F-DB551F24AFC5}"/>
+    <hyperlink ref="B2" r:id="rId5" xr:uid="{CC5280EE-0312-4561-AB50-70EEA85CF75B}"/>
+    <hyperlink ref="C2" r:id="rId6" xr:uid="{E86B0BA0-E1AF-42C9-8A87-FFBED43D1DE1}"/>
+    <hyperlink ref="H2" r:id="rId7" xr:uid="{BAF7D64D-C0BB-43A6-85BE-B26CE103A75E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
